--- a/etf_holdings/2026-08-27_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:34</t>
+          <t>2026-08-27 17:13:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.87%12,000,000</t>
+          <t>17.19%12,000,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16.87%</t>
+          <t>17.19%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:34</t>
+          <t>2026-08-27 17:13:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.7%5500</t>
+          <t>+5.86%3340</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>+5.86%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5500</v>
+        <v>3340</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.80%1,690,000</t>
+          <t>6.25%3,150,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.80%</t>
+          <t>6.25%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1690000</v>
+        <v>3150000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:34</t>
+          <t>2026-08-27 17:13:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+5.86%3340</t>
+          <t>+1.72%1180</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3340</v>
+        <v>1180</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.79%3,150,000</t>
+          <t>5.93%8,460,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.79%</t>
+          <t>5.93%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3150000</v>
+        <v>8460000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:34</t>
+          <t>2026-08-27 17:13:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+1.72%1180</t>
+          <t>-6.7%5500</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1180</v>
+        <v>5500</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.71%8,460,000</t>
+          <t>5.23%1,600,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.71%</t>
+          <t>5.23%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8460000</v>
+        <v>1600000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:34</t>
+          <t>2026-08-27 17:13:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:34</t>
+          <t>2026-08-27 17:13:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-4.05%118.5</t>
+          <t>-1.4%5645</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>118.5</v>
+        <v>5645</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.31%60,000,000</t>
+          <t>3.65%1,087,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.31%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>60000000</v>
+        <v>1087000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:34</t>
+          <t>2026-08-27 17:13:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.4%5645</t>
+          <t>-4.05%118.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-4.05%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5645</v>
+        <v>118.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.62%1,087,000</t>
+          <t>3.52%50,000,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1087000</v>
+        <v>50000000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:34</t>
+          <t>2026-08-27 17:13:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.23%1,100,000</t>
+          <t>3.33%1,100,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:34</t>
+          <t>2026-08-27 17:13:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.06%9,785,000</t>
+          <t>3.23%9,785,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:34</t>
+          <t>2026-08-27 17:13:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.93%2,880,000</t>
+          <t>3.03%2,880,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>3.03%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:34</t>
+          <t>2026-08-27 17:13:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.7%2090</t>
+          <t>+9.94%6915</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2090</v>
+        <v>6915</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.76%2,307,000</t>
+          <t>2.88%700,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.88%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2307000</v>
+        <v>700000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:34</t>
+          <t>2026-08-27 17:13:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.2%605</t>
+          <t>+1.7%2090</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>605</v>
+        <v>2090</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.76%8,000,000</t>
+          <t>2.87%2,307,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>8000000</v>
+        <v>2307000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:34</t>
+          <t>2026-08-27 17:13:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.61%660,000</t>
+          <t>2.67%660,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.67%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:34</t>
+          <t>2026-08-27 17:13:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+3.75%914</t>
+          <t>+2.2%605</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+3.75%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>914</v>
+        <v>605</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.33%4,550,000</t>
+          <t>2.52%7,000,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>4550000</v>
+        <v>7000000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:34</t>
+          <t>2026-08-27 17:13:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+9.94%6915</t>
+          <t>+3.75%914</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+3.75%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6915</v>
+        <v>914</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.29%626,000</t>
+          <t>2.47%4,550,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>626000</v>
+        <v>4550000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:35</t>
+          <t>2026-08-27 17:13:57</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.21%621,000</t>
+          <t>2.19%621,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:35</t>
+          <t>2026-08-27 17:13:57</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.81%2,640,000</t>
+          <t>2.03%2,640,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:35</t>
+          <t>2026-08-27 17:13:57</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-5.56%1445</t>
+          <t>+2.48%186</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>+2.48%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1445</v>
+        <v>186</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.69%1,900,000</t>
+          <t>1.66%15,000,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1900000</v>
+        <v>15000000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:35</t>
+          <t>2026-08-27 17:13:57</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.45%15305</t>
+          <t>-5.56%1445</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.45%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>15305</v>
+        <v>1445</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.64%179,500</t>
+          <t>1.63%1,900,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>179500</v>
+        <v>1900000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:35</t>
+          <t>2026-08-27 17:13:57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+2.48%186</t>
+          <t>-2.45%15305</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>186</v>
+        <v>15305</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.58%15,000,000</t>
+          <t>1.63%179,500</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>15000000</v>
+        <v>179500</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:35</t>
+          <t>2026-08-27 17:13:57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.55%2,800,000</t>
+          <t>1.59%2,800,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:35</t>
+          <t>2026-08-27 17:13:57</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.40%1,200,000</t>
+          <t>1.47%1,200,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:35</t>
+          <t>2026-08-27 17:13:57</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1864,20 +1864,20 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.25%10,358,000</t>
+          <t>1.40%10,378,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>10358000</v>
+        <v>10378000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:35</t>
+          <t>2026-08-27 17:13:57</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.21%1,737,000</t>
+          <t>1.35%1,737,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:35</t>
+          <t>2026-08-27 17:13:57</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.51%1990</t>
+          <t>+9.88%2225</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+9.88%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1990</v>
+        <v>2225</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.15%1,000,000</t>
+          <t>1.24%936,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1000000</v>
+        <v>936000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:35</t>
+          <t>2026-08-27 17:13:57</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+9.88%2225</t>
+          <t>+0.51%1990</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+9.88%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2225</v>
+        <v>1990</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.02%866,000</t>
+          <t>1.18%1,000,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>866000</v>
+        <v>1000000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:35</t>
+          <t>2026-08-27 17:13:57</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.89%5,360,000</t>
+          <t>0.88%5,360,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:35</t>
+          <t>2026-08-27 17:13:57</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.48%130,000</t>
+          <t>0.49%130,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:35</t>
+          <t>2026-08-27 17:13:57</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.46%3,200,000</t>
+          <t>0.48%3,200,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:35</t>
+          <t>2026-08-27 17:13:57</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.42%2,000,000</t>
+          <t>0.47%2,000,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:37</t>
+          <t>2026-08-27 17:13:58</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.35%800,000</t>
+          <t>0.36%800,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:37</t>
+          <t>2026-08-27 17:13:58</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.33%4,500,000</t>
+          <t>0.34%4,500,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:37</t>
+          <t>2026-08-27 17:13:58</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:37</t>
+          <t>2026-08-27 17:13:58</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:37</t>
+          <t>2026-08-27 17:13:58</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.93%1595</t>
+          <t>+9.9%494</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>+9.9%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1595</v>
+        <v>494</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.21%225,000</t>
+          <t>0.23%800,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>225000</v>
+        <v>800000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:37</t>
+          <t>2026-08-27 17:13:58</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+9.9%494</t>
+          <t>-0.93%1595</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+9.9%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>494</v>
+        <v>1595</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.21%800,000</t>
+          <t>0.21%225,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>800000</v>
+        <v>225000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:37</t>
+          <t>2026-08-27 17:13:58</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,25 +2700,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1560中砂</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+1.17%690</t>
+          <t>-0.46%1075</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>690</v>
+        <v>1075</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.16%393,000</t>
+          <t>0.16%250,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2727,11 +2727,11 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>393000</v>
+        <v>250000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:37</t>
+          <t>2026-08-27 17:13:58</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>3450聯鈞</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.46%1075</t>
+          <t>+0.7%578</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1075</v>
+        <v>578</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.16%250,000</t>
+          <t>0.14%400,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>250000</v>
+        <v>400000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:37</t>
+          <t>2026-08-27 17:13:58</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>1560中砂</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+5.3%477</t>
+          <t>+1.17%690</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+5.3%</t>
+          <t>+1.17%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>477</v>
+        <v>690</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.13%500,000</t>
+          <t>0.12%300,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:37</t>
+          <t>2026-08-27 17:13:58</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>1717長興</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.7%578</t>
+          <t>+5.42%75.8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>+5.42%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>578</v>
+        <v>75.8</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.13%400,000</t>
+          <t>0.11%2,500,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>400000</v>
+        <v>2500000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:37</t>
+          <t>2026-08-27 17:13:58</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1717長興</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+5.42%75.8</t>
+          <t>+0.92%219.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+5.42%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>75.8</v>
+        <v>219.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.10%2,500,000</t>
+          <t>0.09%700,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>2500000</v>
+        <v>700000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:37</t>
+          <t>2026-08-27 17:13:58</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,34 +3005,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>4966譜瑞-KY</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.92%219.5</t>
+          <t>+2.43%590</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>+2.43%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>219.5</v>
+        <v>590</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.09%700,000</t>
+          <t>0.08%220,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>700000</v>
+        <v>220000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:37</t>
+          <t>2026-08-27 17:13:58</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,34 +3066,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4966譜瑞-KY</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+2.43%590</t>
+          <t>+1.24%245</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+2.43%</t>
+          <t>+1.24%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>590</v>
+        <v>245</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.07%220,000</t>
+          <t>0.05%350,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>220000</v>
+        <v>350000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:37</t>
+          <t>2026-08-27 17:13:58</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.24%245</t>
+          <t>+1.17%433</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.24%</t>
+          <t>+1.17%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>245</v>
+        <v>433</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.05%350,000</t>
+          <t>0.05%200,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>350000</v>
+        <v>200000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:37</t>
+          <t>2026-08-27 17:13:58</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,34 +3188,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+1.17%433</t>
+          <t>+1.41%2155</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>433</v>
+        <v>2155</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.05%200,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>200000</v>
+        <v>1000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:38</t>
+          <t>2026-08-27 17:14:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,21 +3249,21 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+1.41%2155</t>
+          <t>-0.5%497.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2155</v>
+        <v>497.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:38</t>
+          <t>2026-08-27 17:14:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,21 +3310,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.5%497.5</t>
+          <t>+5.3%477</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>+5.3%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>497.5</v>
+        <v>477</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:38</t>
+          <t>2026-08-27 17:14:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:38</t>
+          <t>2026-08-27 17:14:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:38</t>
+          <t>2026-08-27 17:14:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-27_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:56</t>
+          <t>2026-08-27 19:37:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:56</t>
+          <t>2026-08-27 19:37:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:56</t>
+          <t>2026-08-27 19:37:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:56</t>
+          <t>2026-08-27 19:37:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:56</t>
+          <t>2026-08-27 19:37:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:56</t>
+          <t>2026-08-27 19:37:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:56</t>
+          <t>2026-08-27 19:37:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:56</t>
+          <t>2026-08-27 19:37:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:56</t>
+          <t>2026-08-27 19:37:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:56</t>
+          <t>2026-08-27 19:37:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:56</t>
+          <t>2026-08-27 19:37:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:56</t>
+          <t>2026-08-27 19:37:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:56</t>
+          <t>2026-08-27 19:37:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:56</t>
+          <t>2026-08-27 19:37:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:56</t>
+          <t>2026-08-27 19:37:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:57</t>
+          <t>2026-08-27 19:37:58</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:57</t>
+          <t>2026-08-27 19:37:58</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:57</t>
+          <t>2026-08-27 19:37:58</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:57</t>
+          <t>2026-08-27 19:37:58</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:57</t>
+          <t>2026-08-27 19:37:58</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:57</t>
+          <t>2026-08-27 19:37:58</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:57</t>
+          <t>2026-08-27 19:37:58</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:57</t>
+          <t>2026-08-27 19:37:58</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:57</t>
+          <t>2026-08-27 19:37:58</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:57</t>
+          <t>2026-08-27 19:37:58</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:57</t>
+          <t>2026-08-27 19:37:58</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:57</t>
+          <t>2026-08-27 19:37:58</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:57</t>
+          <t>2026-08-27 19:37:58</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:57</t>
+          <t>2026-08-27 19:37:58</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:57</t>
+          <t>2026-08-27 19:37:58</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:58</t>
+          <t>2026-08-27 19:37:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:58</t>
+          <t>2026-08-27 19:37:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:58</t>
+          <t>2026-08-27 19:37:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:58</t>
+          <t>2026-08-27 19:37:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:58</t>
+          <t>2026-08-27 19:37:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:58</t>
+          <t>2026-08-27 19:37:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:58</t>
+          <t>2026-08-27 19:37:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:58</t>
+          <t>2026-08-27 19:37:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:58</t>
+          <t>2026-08-27 19:37:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:58</t>
+          <t>2026-08-27 19:37:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:58</t>
+          <t>2026-08-27 19:37:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:58</t>
+          <t>2026-08-27 19:37:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:58</t>
+          <t>2026-08-27 19:37:59</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:58</t>
+          <t>2026-08-27 19:37:59</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:58</t>
+          <t>2026-08-27 19:37:59</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:00</t>
+          <t>2026-08-27 19:38:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:00</t>
+          <t>2026-08-27 19:38:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:00</t>
+          <t>2026-08-27 19:38:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:00</t>
+          <t>2026-08-27 19:38:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:00</t>
+          <t>2026-08-27 19:38:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
